--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/phi-4/default/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/phi-4/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H3">
         <v>426</v>
